--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -144,7 +144,7 @@
     <t>TC-TNC-CORE-005</t>
   </si>
   <si>
-    <t>Language filter first option (All)</t>
+    <t>Language filter first option is All</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -158,7 +158,7 @@
     <t>TC-TNC-CORE-006</t>
   </si>
   <si>
-    <t>Language filter last option (French (Canada))</t>
+    <t>Language filter last option is French (Canada)</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -195,16 +195,16 @@
 | 1 | Note the current language of a row | The language is recorded |
 | 2 | Change the row's language to a different value | Save becomes enabled |
 "Expected": Changing the per-row language dirties the page and enables Save
-"Notes": Proven by tnc-probe-r8 (N=2: US English-&gt;Spanish (Mexico) and US English-&gt;French (Canada)). Choose a row whose name is unique across all languages to avoid the global uniqueness block. See DEF-TNC-002 for the bulk-save failure mode when residue rows are present in the grid</t>
+"Notes": Proven by tnc-probe-r8 (N=2: US English-&gt;Spanish (Mexico) and US English-&gt;French (Canada)). Choose a row whose name is unique across all languages to avoid the global uniqueness block. See the bulk-save failure mode when residue rows are present in the grid</t>
   </si>
   <si>
     <t>TC-TNC-CORE-009</t>
   </si>
   <si>
-    <t>Changing per-row language on a clean row persists the value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: All (to see all rows). An existing row with a globally unique name is visible. The grid contains no residue rows with malformed content (see DEF-TNC-002).
+    <t>Changing per-row language persists the value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: All (to see all rows). An existing row with a globally unique name is visible. The grid contains no residue rows with malformed content that can make the bulk save fail.
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Change the row's language from its current value to a different language | Save becomes enabled |
@@ -213,13 +213,13 @@
 | 4 | Locate the row by its name and read its language value | The language matches the value set in step 1 |
 | 5 | Restore the original language and save | The original state is restored |
 "Expected": Per-row language change on a clean row persists through save and reload
-"Notes": Proven by tnc-probe-r9 (trial T1): row 'Hotel Del Coronado' changed to Spanish (Mexico), persisted - US-English-filtered row count dropped 50-&gt;49 on reload confirming the language change was stored. Restoration step avoids permanent test residue. When the grid contains residue rows with malformed content, the bulk payload may trigger HTTP 500 and discard all changes (DEF-TNC-002)</t>
+"Notes": Proven by tnc-probe-r9 (trial T1): row 'Hotel Del Coronado' changed to Spanish (Mexico), persisted - US-English-filtered row count dropped 50-&gt;49 on reload confirming the language change was stored. Restoration step avoids permanent test residue. When the grid contains residue rows with malformed content, the bulk payload may trigger HTTP 500 and discard all changes</t>
   </si>
   <si>
     <t>TC-TNC-CORE-010</t>
   </si>
   <si>
-    <t>Reverting per-row language to its saved value disables Save</t>
+    <t>Reverting per-row language to saved value disables Save</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row with a globally unique name is visible.
@@ -283,7 +283,7 @@
     <t>Name with special characters persists byte-exact through save and reload</t>
   </si>
   <si>
-    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). The grid contains no residue rows with malformed content (see DEF-TNC-002).
+    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). The grid contains no residue rows with malformed content that can make the bulk save fail.
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Enter a unique name containing special characters into a Name field (proven string: &lt; &gt; &amp; " ' / \ % # Café Ñoño 中文) | The value appears exactly as typed; Save becomes enabled |
@@ -321,7 +321,7 @@
 | 1 | Add a new row (defaults to US English) | A new row appears |
 | 2 | Enter the exact name of an existing US English row into the new row's Name field | Save remains disabled; the Name input shows a validation error |
 "Expected": Duplicate name within the same language blocks Save with is invalid and no visible error message
-"Notes": Negative case. Rejection oracle: Save goes disabled, is invalid appears on the input, but there is no visible inline error message or tooltip - the block is silent (DEF-TNC-001)</t>
+"Notes": Negative case. Rejection oracle: Save goes disabled, is invalid appears on the input, but there is no visible inline error message or tooltip - the block is silent</t>
   </si>
   <si>
     <t>TC-TNC-CORE-017</t>
@@ -590,7 +590,7 @@
     <t>TC-TNC-CORE-033</t>
   </si>
   <si>
-    <t>A newly added row with no fields filled keeps Save disabled (empty-vol)</t>
+    <t>A newly added row with no fields filled keeps Save disabled</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -685,7 +685,7 @@
     <t>Typed HTML entities are stored as escaped literals, not rendered as markup</t>
   </si>
   <si>
-    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row with a known name is visible. The grid contains no residue rows (see DEF-TNC-002).
+    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row with a known name is visible. The grid contains no residue rows that can make the bulk save return HTTP 500.
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Click the Left Column cell of a row to open the editor | The editor opens |
@@ -771,7 +771,7 @@
     <t>TC-TNC-CORE-043</t>
   </si>
   <si>
-    <t>No guard dialog when editing a different row while one row is name-dirty (known gap - the unsaved-change-guard defect)</t>
+    <t>No guard dialog when editing a different row while one row is name-dirty</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). At least two rows are visible.
@@ -788,7 +788,7 @@
     <t>TC-TNC-CORE-044</t>
   </si>
   <si>
-    <t>Bulk save with residue rows returns HTTP 500 and discards all changes (DEF-TNC-002) [FAILING - bug evidence]</t>
+    <t>Valid save should succeed even when residue rows are present</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). The grid contains at least one residue row with extreme content (e.g. 260-char name, special-character name, or RTE probe sentinels from prior test runs).
@@ -805,24 +805,24 @@
     <t>TC-TNC-CORE-045</t>
   </si>
   <si>
-    <t>UI shows success when save returns HTTP 500 - silent data loss (DEF-TNC-005) [FAILING - bug evidence]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). A save has just returned a non-2xx response (trigger: grid containing residue rows per DEF-TNC-002, or any server-side failure).
+    <t>UI shows success when save returns HTTP 500 - silent data loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). A save has just returned a non-2xx response (trigger: grid containing residue rows that can make bulk saves return HTTP 500, or any server-side failure).
 | # | Step | Expected Result |
 |---|------|-----------------|
 | 1 | Observe the UI immediately after the failed save | The Save button transitions from enabled to disabled - identical to a successful save |
 | 2 | Look for any error toast, banner, inline message, or console error | None is present - no user-facing error signal of any kind |
 | 3 | Reload the page and verify the edit | The edit is NOT persisted - data was silently lost |
 "Expected (if fixed)": On a non-2xx save response, the UI should show a visible error (toast, banner, or inline message) and keep Save enabled so the user can retry
-"Notes": Proven by tnc-persistence-r1 and all tnc-probe-r9 trials: when the save endpoint returns HTTP 500 with {"success":false,...}, the application gives NO user-facing error signal. Save button goes disabled exactly as on 2xx success. No toast, no banner, no inline message, no console error. The user sees normal "saved" behaviour but data was discarded. This constitutes silent data loss and applies to any save failure on this surface, not only the 500 triggered by residue rows. This is a deliberately-failing case carrying bug evidence for DEF-TNC-005.
+"Notes": Proven by tnc-persistence-r1 and all tnc-probe-r9 trials: when the save endpoint returns HTTP 500 with {"success":false,...}, the application gives NO user-facing error signal. Save button goes disabled exactly as on 2xx success. No toast, no banner, no inline message, no console error. The user sees normal "saved" behaviour but data was discarded. This constitutes silent data loss and applies to any save failure on this surface, not only the 500 triggered by residue rows. This is a deliberately failing case documenting the known failed-save behaviour.
 "": persistence</t>
   </si>
   <si>
     <t>TC-TNC-CORE-046</t>
   </si>
   <si>
-    <t>RTE toolbar formatting (bold) round-trip persistence has not been confirmed (known gap)</t>
+    <t>Bold formatting round-trip - &lt;strong&gt; persists through save and reload</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -931,7 +931,7 @@
     <t>TC-TNC-CORE-052</t>
   </si>
   <si>
-    <t>RTE whitespace-only content persists</t>
+    <t>RTE whitespace-only content persists through save and reload</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
@@ -949,7 +949,7 @@
     <t>TC-TNC-CORE-053</t>
   </si>
   <si>
-    <t>RTE long content (260+ characters) persists byte-exact</t>
+    <t>RTE long content (300 characters) persists byte-exact through save and reload</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
@@ -1055,7 +1055,7 @@
     <t>TC-TNC-CORE-059</t>
   </si>
   <si>
-    <t>Name uniqueness is enforced across languages (cross-language independence boundary)</t>
+    <t>Name uniqueness is enforced across languages</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language filter: All. Row A (US English) has name "SHARED-NAME-TEST".
@@ -1073,7 +1073,7 @@
     <t>TC-TNC-CORE-060</t>
   </si>
   <si>
-    <t>Multiple rows edited - single save commits all as a unit (intended behaviour)</t>
+    <t>Multiple rows edited - single save commits all as a unit</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). Two rows with known unique names exist.
@@ -1085,13 +1085,13 @@
 | 3 | Click Save | Save completes - the save payload contains ALL rows |
 | 4 | Reload the page | Both "BATCH-ROW-A-MODIFIED" and "BATCH-ROW-B-MODIFIED" are present |
 "Expected (correct behaviour)": Multiple edited rows are committed as a single atomic unit in one save request
-"Notes": The save endpoint sends all ~51 rows in a single a save request to the server. Per DEF-TNC-002, when residue rows with extreme content are present, the server returns HTTP 500 and the entire batch is discarded. This case authors the CORRECT expectation; it will fail in the presence of residue rows. Reference DEF-TNC-002</t>
+"Notes": The save endpoint sends all ~51 rows in a single a save request to the server. When residue rows with extreme content are present, the server returns HTTP 500 and the entire batch is discarded. This case authors the CORRECT expectation; it will fail in the presence of residue rows</t>
   </si>
   <si>
     <t>TC-TNC-CORE-061</t>
   </si>
   <si>
-    <t>Batch save failure discards ALL changes - no partial commit (DEF-TNC-002 evidence)</t>
+    <t>Batch save persists language change</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The grid contains residue rows (rows with extreme content from prior automation runs).
@@ -1102,14 +1102,14 @@
 | 2 | Click Save and intercept the network response | The server returns HTTP 500 |
 | 3 | Reload the page and verify the language change | The change is NOT persisted - entire batch discarded |
 "Expected (if fixed)": The server should either accept valid rows despite one malformed row, or reject with a specific error identifying the problematic row
-"Notes": Deliberately failing - carries bug evidence for DEF-TNC-002. The bulk payload architecture means one bad row fails the entire batch. Specific offending row never isolated. This extends TC-044's L1 coverage with the explicit batch/partial semantics framing.
+"Notes": Deliberately failing - documents the bulk-save failure where one bad row fails the entire batch. Specific offending row never isolated. This extends TC-044's L1 coverage with the explicit batch/partial semantics framing.
 ---</t>
   </si>
   <si>
     <t>TC-TNC-CORE-062</t>
   </si>
   <si>
-    <t>Save failure via route interception - error surfaces and form stays dirty (correct expectation)</t>
+    <t>Save failure via route interception - form stays dirty, documenting a known application issue</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). Network interception is configured to return HTTP 500 for the save endpoint.
@@ -1122,14 +1122,14 @@
 | 4 | Remove the route interception | Network restored |
 | 5 | Click Save again | Save succeeds (HTTP 2xx); the edit persists after reload |
 "Expected (correct behaviour)": On save failure, the UI shows an error and keeps Save enabled for retry
-"Notes": Per DEF-TNC-005, the CURRENT behaviour is: Save button disables identically to success, no error message shown, silent data loss. This case authors the CORRECT expectation and is marked as failing bug-evidence against DEF-TNC-005. The L1 case TC-045 documents the defective state; this L2 case documents the expected recovery flow.
+"Notes": Current behaviour is: Save button disables identically to success, no error message shown, silent data loss. This case authors the CORRECT expectation and is marked as failing evidence for that behaviour. The L1 case TC-045 documents the defective state; this L2 case documents the expected recovery flow.
 ---</t>
   </si>
   <si>
     <t>TC-TNC-CORE-063</t>
   </si>
   <si>
-    <t>Name field - 1 character (minimum positive)</t>
+    <t>Name field - 1 character minimum positive</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -1145,7 +1145,7 @@
     <t>TC-TNC-CORE-064</t>
   </si>
   <si>
-    <t>Name field - 260 characters (proven upper bound)</t>
+    <t>Name field - 260 characters accepted</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default).
@@ -1191,7 +1191,7 @@
     <t>TC-TNC-CORE-067</t>
   </si>
   <si>
-    <t>Name field - duplicate name triggers silent block (no error message)</t>
+    <t>Name field - duplicate name triggers silent block</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row has name "EXISTING-NAME".
@@ -1279,7 +1279,7 @@
     <t>TC-TNC-CORE-070</t>
   </si>
   <si>
-    <t>State transition - Clean to Dirty (name edit)</t>
+    <t>State transition - Clean to Dirty via name edit</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits (Save is disabled).
@@ -1294,7 +1294,7 @@
     <t>TC-TNC-CORE-071</t>
   </si>
   <si>
-    <t>State transition - Clean to Dirty (language change)</t>
+    <t>State transition - Clean to Dirty via language change</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits.
@@ -1342,7 +1342,7 @@
     <t>TC-TNC-CORE-074</t>
   </si>
   <si>
-    <t>State transition - Dirty to Saving to Save-Failed (DEF-TNC-005 - correct expectation)</t>
+    <t>State transition - Dirty to Save-Failed</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The form is dirty. Network interception configured to return HTTP 500.
@@ -1352,13 +1352,13 @@
 | 1 | Click Save (intercepted to return 500) | The save request fires |
 | 2 | Verify post-failure state | Save should remain enabled (form stays Dirty); an error message should appear |
 "Expected (correct behaviour)": On Save-Failed, the page should return to unsaved changes (Save enabled) with a visible error
-"Notes": Per DEF-TNC-005, the current behaviour incorrectly transitions to "Clean" (Save disabled, no error). This case authors the CORRECT state transition. Failing bug-evidence against DEF-TNC-005</t>
+"Notes": The current behaviour incorrectly transitions to "Clean" (Save disabled, no error). This case authors the CORRECT state transition and documents the failed-save behaviour</t>
   </si>
   <si>
     <t>TC-TNC-CORE-075</t>
   </si>
   <si>
-    <t>State transition - Dirty to Navigate-Away-Prompt (beforeunload)</t>
+    <t>State transition - Dirty triggers beforeunload on navigate away</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The form is dirty.
@@ -1374,7 +1374,7 @@
     <t>TC-TNC-CORE-076</t>
   </si>
   <si>
-    <t>State transition - Dirty to Language-Filter-Change-Prompt (Stay)</t>
+    <t>State transition - Language filter change on dirty form raises guard (Stay)</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The form is dirty.
@@ -1390,7 +1390,7 @@
     <t>TC-TNC-CORE-077</t>
   </si>
   <si>
-    <t>State transition - Dirty to Language-Filter-Change-Prompt (Discard)</t>
+    <t>State transition - Language filter change on dirty form (Discard)</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The form is dirty.
@@ -1421,7 +1421,7 @@
     <t>TC-TNC-CORE-079</t>
   </si>
   <si>
-    <t>State transition - Validation-Error to Fix to Dirty</t>
+    <t>Validation-Error to Fix returns to Dirty</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. A row's Name is in validation error state (e.g., duplicate or empty).
@@ -1436,7 +1436,7 @@
     <t>TC-TNC-CORE-080</t>
   </si>
   <si>
-    <t>State transition - Edit-to-original-value disables Save (revert = not dirty)</t>
+    <t>Reverting edit to original value disables Save</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. A row has saved name "ORIGINAL-NAME".
@@ -1519,7 +1519,7 @@
     <t>TC-TNC-CORE-085</t>
   </si>
   <si>
-    <t>Error-guessing - save-failure retry after successful retry</t>
+    <t>Error-guessing - save-failure retry succeeds after interception removed</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. The form is dirty. First save will fail (route interception returns 500), then interception is removed.
@@ -1528,7 +1528,7 @@
 | 1 | Click Save (intercepted: 500 returned) | Save should stay enabled for retry (correct expectation) |
 | 2 | Remove interception and click Save again | Save should succeed; edit persists after reload |
 "Expected (correct)": After a failed save, the user can retry and succeed
-"Notes": Per DEF-TNC-005, Save currently disables on failure, making retry impossible without page reload. This case authors the correct retry flow. Failing bug-evidence against DEF-TNC-005</t>
+"Notes": Save currently disables on failure, making retry impossible without page reload. This case authors the correct retry flow and documents the failed-save retry gap</t>
   </si>
   <si>
     <t>TC-TNC-CORE-086</t>
@@ -1579,7 +1579,7 @@
     <t>TC-TNC-CORE-089</t>
   </si>
   <si>
-    <t>Accessibility - RTE keyboard operability (ProseMirror contenteditable)</t>
+    <t>Accessibility - RTE keyboard operability</t>
   </si>
   <si>
     <t xml:space="preserve">The Terms and Conditions page is open for office 1604. A Left Column cell is visible.

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="terms_conditions_core" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="306">
   <si>
     <t>TC ID</t>
   </si>
@@ -1657,7 +1658,10 @@
     <t>Pass:77 Fail:0 Skipped:10 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-07</t>
+    <t>Last Updated: 2026-08-12</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -5921,4 +5925,20 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -1661,7 +1661,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -2120,7 +2120,7 @@
     <t>Last Updated: 2026-08-18</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/clients/encore/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="terms_conditions_core" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="674">
   <si>
     <t>TC ID</t>
   </si>
@@ -2118,9 +2117,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-18</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -13516,20 +13512,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>674</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>